--- a/Workflows/Chemical validation/Level0_Templates/XXXX_XX_ANIONS.xlsx
+++ b/Workflows/Chemical validation/Level0_Templates/XXXX_XX_ANIONS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecnun365-my.sharepoint.com/personal/jtorrens_unav_es/Documents/Documentos/LICA/data/plantillas/Forest/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jtorrens\ICP\repoGitLab\lifewatch-vre\Workflows\Chemical validation\Level0_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="8_{AE7C82AE-8C8D-4882-9E7D-A823FAA85301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AA6F817-4529-40E5-AEE3-9D701DE52935}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F5C08B-1008-44ED-B98E-793ADEC59EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3FD923B0-A352-4B39-804E-C5D1C21F4722}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3FD923B0-A352-4B39-804E-C5D1C21F4722}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>SampleID</t>
   </si>
@@ -59,213 +59,6 @@
   </si>
   <si>
     <t>PO4(mg/l)</t>
-  </si>
-  <si>
-    <t>05PS INT</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>Valsain</t>
-  </si>
-  <si>
-    <t>05PS INT NIEVE</t>
-  </si>
-  <si>
-    <t>05PS INT LIX 20</t>
-  </si>
-  <si>
-    <t>05PS INT LIX 60</t>
-  </si>
-  <si>
-    <t>05PS INT LIX G 20</t>
-  </si>
-  <si>
-    <t>05PS INT LIX G 60</t>
-  </si>
-  <si>
-    <t>05PS EXT</t>
-  </si>
-  <si>
-    <t>05PS EXT NIEVE</t>
-  </si>
-  <si>
-    <t>06QI INT</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>Morella</t>
-  </si>
-  <si>
-    <t>06QI EXT</t>
-  </si>
-  <si>
-    <t>07QI INT</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>Majadas</t>
-  </si>
-  <si>
-    <t>07QI EXT</t>
-  </si>
-  <si>
-    <t>10PPA INT</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Almonte</t>
-  </si>
-  <si>
-    <t>10PPA EXT</t>
-  </si>
-  <si>
-    <t>11QS INT</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Villanueva de la Sierra</t>
-  </si>
-  <si>
-    <t>11QS EXT</t>
-  </si>
-  <si>
-    <t>22PN INT</t>
-  </si>
-  <si>
-    <t>Mora de Rubielos</t>
-  </si>
-  <si>
-    <t>22PN INT NIEVE</t>
-  </si>
-  <si>
-    <t>22PN EXT</t>
-  </si>
-  <si>
-    <t>22PN EXT NIEVE</t>
-  </si>
-  <si>
-    <t>25PH INT</t>
-  </si>
-  <si>
-    <t>Tibi</t>
-  </si>
-  <si>
-    <t>25PH EXT</t>
-  </si>
-  <si>
-    <t>26QI INT</t>
-  </si>
-  <si>
-    <t>Andujar</t>
-  </si>
-  <si>
-    <t>26QI EXT</t>
-  </si>
-  <si>
-    <t>30PS INT</t>
-  </si>
-  <si>
-    <t>Soria</t>
-  </si>
-  <si>
-    <t>30PS INT NIEVE</t>
-  </si>
-  <si>
-    <t>30PS INT LIX 20</t>
-  </si>
-  <si>
-    <t>30PS INT LIX 60</t>
-  </si>
-  <si>
-    <t>30PS EXT</t>
-  </si>
-  <si>
-    <t>30PS EXT NIEVE</t>
-  </si>
-  <si>
-    <t>33QPE INT</t>
-  </si>
-  <si>
-    <t>Cervera de Pisuerga</t>
-  </si>
-  <si>
-    <t>33QPE INT NIEVE</t>
-  </si>
-  <si>
-    <t>33QPE INT LIX 20</t>
-  </si>
-  <si>
-    <t>33QPE INT LIX 60</t>
-  </si>
-  <si>
-    <t>33QPE EXT</t>
-  </si>
-  <si>
-    <t>33QPE EXT NIEVE</t>
-  </si>
-  <si>
-    <t>37PPR INT</t>
-  </si>
-  <si>
-    <t>Cuellar</t>
-  </si>
-  <si>
-    <t>37PPR EXT</t>
-  </si>
-  <si>
-    <t>54PH INT</t>
-  </si>
-  <si>
-    <t>El Saler</t>
-  </si>
-  <si>
-    <t>54PH EXT</t>
-  </si>
-  <si>
-    <t>102PPR INT</t>
-  </si>
-  <si>
-    <t>Padron</t>
-  </si>
-  <si>
-    <t>102PPR INT LIX 20</t>
-  </si>
-  <si>
-    <t>102PPR INT LIX 60</t>
-  </si>
-  <si>
-    <t>102PPR EXT</t>
-  </si>
-  <si>
-    <t>115FS INT</t>
-  </si>
-  <si>
-    <t>Burguete</t>
-  </si>
-  <si>
-    <t>115FS INT NIEVE</t>
-  </si>
-  <si>
-    <t>115FS INT LIX 20</t>
-  </si>
-  <si>
-    <t>115FS INT LIX 60</t>
-  </si>
-  <si>
-    <t>115FS EXT</t>
-  </si>
-  <si>
-    <t>115FS EXT NIEVE</t>
   </si>
   <si>
     <t>Comments</t>
@@ -391,13 +184,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -412,8 +205,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="95250" y="76200"/>
-          <a:ext cx="12011025" cy="5772150"/>
+          <a:off x="95250" y="76199"/>
+          <a:ext cx="12011025" cy="12525376"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -451,170 +244,1919 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="sng"/>
-            <a:t>PLANTILLA ANIONS</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400"/>
-            <a:t>Esto es la plantilla (XXXX_XX_ES02_ANIONS.xlsx) para </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1"/>
-            <a:t>rellenar los datos de ANIONS en la hoja data</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400"/>
-            <a:t>. Para cada año y mes se debe rellenar la plantilla una vez. Es IMPORTANTE nombrar la plantilla con el año y mes que corresponde, cambiando las XXXX_XX por el año y mes en cuestión (ej: 2023_06_ES02_ANIONS.xlsx). La idea es copiar en esta plantilla los datos que se han logrado en el laboratorio. No es necesario eliminar ninguna fila, y si falta un dato o se ha obtenido un dato erróneo, no añadirlo y dejar la celda vacía.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400"/>
-            <a:t>Columnas:</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1"/>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>TEMPLATE: XXXX_XX_ANIONS.xlsx</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>PURPOSE:</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>This template records the major anion concentrations measured in water samples. One row per analytical sample. The same template is used for all subprogrammes.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>FILE NAMING CONVENTION:</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>YYYY_MM_ANIONS.xlsx     — original analysis</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>YYYY_MM_ANIONS_REP.xlsx — repeated analysis</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Where YYYY = year, MM = month of collection. If differente years or months are collected in the same template, you could</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>keep XX.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>COLUMNS:</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>SampleID</a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400"/>
-            <a:t>: identificador único para los diferentes puntos de muestreo en las parcelas de estudio en la región de muestreo. Cada parcela corresponde a un subprograma de ICPIM.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1"/>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Unique identifier for the analytical sample. This is the key that links this template to all other templates and to the samplesInfo.xlsx metadata file.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Use the standardised ICP sample code for the plot and subprogramme. The code combines the plot number, the species abbreviation, the collection type (INT = interior/throughfall, EXT = exterior/bulk deposition) and any additional qualifier: INT         = throughfall (interior of the forest) EXT         = bulk open-field deposition (exterior) NIEVE       = snow sample LIX 20      = soil lysimeter at 20 cm depth LIX 60      = soil lysimeter at 60 cm depth LIX G 20    = gravity lysimeter at 20 cm depth LIX G 60    = gravity lysimeter at 60 cm depth</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>05PS INT, 22PN EXT NIEVE, 30PS INT LIX 20, 115FS EXT</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty. Must be identical across all templates for the same sample in the same month.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SiteCode</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Numeric code identifying the monitoring plot.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Use the official ICP plot number (e.g. 05, 22, 115). Do not include leading zeros beyond the standard format.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>05, 06, 22, 102, 115</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>SiteName</a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400"/>
-            <a:t>: nombre de donde se encuentran las muestras de trabajo.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1"/>
-            <a:t>PlotCode</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400"/>
-            <a:t>: codigo de la zona donde se encuentran las muestras de trabajo.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1"/>
-            <a:t>ScodeICPIM</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400"/>
-            <a:t>: codigo del tipo de parcela. Este codigo tambien corresponde al subprograma, ya que cada tipo de parcela corresponde a un subpograma de ICPIM diferente.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1"/>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Name of the monitoring plot or location.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Use the official name of the plot (e.g. Valsain, Bertiz).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Valsain, Mora de Rubielos, Burguete</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>StartDate</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Date on which sample collection began (start of the accumulation period for the collector).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Format DD/MM/YYYY. Leave empty if not recorded.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>01/01/2025, 15/03/2025</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>EndDate</a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400"/>
-            <a:t>: fecha del día en el que se ha recogido la muestra. Formato: dd/mm/YYYY</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1"/>
-            <a:t>CL(mg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400"/>
-            <a:t>Cl calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1"/>
-            <a:t>NO3(mg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400"/>
-            <a:t>NO3 calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1"/>
-            <a:t>SO4(mg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400"/>
-            <a:t>SO4 calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1"/>
-            <a:t>PO4(mg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400"/>
-            <a:t>PO4 calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400"/>
-            <a:t>En este caso se realiza una plantillla para cada mes del año, 12 plantillas diferentes.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400"/>
-            <a:t>MUCHAS GRACIAS POR EL ESFUERZO Y COLABORACIÓN!!</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400"/>
-            <a:t>CUALQUIER DUDA NO DUDEIS EN PREGUNTARME (jtorrens@unav.es)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" b="0" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" b="1" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400"/>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Date on which sample collection ended (date the collector was retrieved and the sample taken to the lab).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Format DD/MM/YYYY.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>31/01/2025, 28/02/2025</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>year</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Year of collection (integer).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Four-digit year. Must match the YYYY in the filename.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2024, 2025</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>month</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Month of collection (integer, 1–12).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Numeric month without leading zero.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1, 6, 12</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>CL(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Chloride concentration in mg/L.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Enter the numeric value from the laboratory report. Chloride is a conservative tracer of marine and road-salt inputs.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1.45, 0.82, 3.10</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>NO3(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Nitrate concentration in mg/L (reported as NO3, not as N).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Enter the value as NO3 in mg/L. The workflow converts automatically to NO3-N when needed.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.58, 1.20, 0.03</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SO4(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Sulphate concentration in mg/L (reported as SO4, not as S).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Enter the value as SO4 in mg/L.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.38, 2.45, 0.10</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>PO4(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Phosphate concentration in mg/L (reported as PO4, not as P).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Enter the value as PO4 in mg/L. Often below detection limit in precipitation and throughfall samples.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.01, 0.05</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Comments</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Free-text field for any relevant observation about this sample.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Note any anomalies, collection issues, or observations that may affect data interpretation (e.g. "collector contaminated", "sample collected one week late", "snow sample mixed with rain"). Leave empty if nothing to report.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -920,7 +2462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1DD1C9D-C8E5-4B60-A994-86B75D81D72C}">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="11.42578125" style="1"/>
@@ -1484,9 +3026,1252 @@
       <c r="O31" s="6"/>
       <c r="P31" s="6"/>
     </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
+      <c r="P38" s="6"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+      <c r="P39" s="6"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
+      <c r="P40" s="6"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="6"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
+      <c r="P42" s="6"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
+      <c r="P43" s="6"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="6"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
+      <c r="O45" s="6"/>
+      <c r="P45" s="6"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6"/>
+      <c r="P46" s="6"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
+      <c r="P47" s="6"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6"/>
+      <c r="P48" s="6"/>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="6"/>
+      <c r="P49" s="6"/>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="6"/>
+      <c r="O50" s="6"/>
+      <c r="P50" s="6"/>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="6"/>
+      <c r="O51" s="6"/>
+      <c r="P51" s="6"/>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
+      <c r="N52" s="6"/>
+      <c r="O52" s="6"/>
+      <c r="P52" s="6"/>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="6"/>
+      <c r="O53" s="6"/>
+      <c r="P53" s="6"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="6"/>
+      <c r="O54" s="6"/>
+      <c r="P54" s="6"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A55" s="6"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="6"/>
+      <c r="O55" s="6"/>
+      <c r="P55" s="6"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A56" s="6"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+      <c r="N56" s="6"/>
+      <c r="O56" s="6"/>
+      <c r="P56" s="6"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A57" s="6"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="6"/>
+      <c r="O57" s="6"/>
+      <c r="P57" s="6"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A58" s="6"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="6"/>
+      <c r="N58" s="6"/>
+      <c r="O58" s="6"/>
+      <c r="P58" s="6"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A59" s="6"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="6"/>
+      <c r="O59" s="6"/>
+      <c r="P59" s="6"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="6"/>
+      <c r="O60" s="6"/>
+      <c r="P60" s="6"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A61" s="6"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="6"/>
+      <c r="O61" s="6"/>
+      <c r="P61" s="6"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" s="6"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="6"/>
+      <c r="O62" s="6"/>
+      <c r="P62" s="6"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
+      <c r="N63" s="6"/>
+      <c r="O63" s="6"/>
+      <c r="P63" s="6"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
+      <c r="M64" s="6"/>
+      <c r="N64" s="6"/>
+      <c r="O64" s="6"/>
+      <c r="P64" s="6"/>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" s="6"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="6"/>
+      <c r="N65" s="6"/>
+      <c r="O65" s="6"/>
+      <c r="P65" s="6"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" s="6"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="6"/>
+      <c r="O66" s="6"/>
+      <c r="P66" s="6"/>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" s="6"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="6"/>
+      <c r="N67" s="6"/>
+      <c r="O67" s="6"/>
+      <c r="P67" s="6"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
+      <c r="M68" s="6"/>
+      <c r="N68" s="6"/>
+      <c r="O68" s="6"/>
+      <c r="P68" s="6"/>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
+      <c r="M69" s="6"/>
+      <c r="N69" s="6"/>
+      <c r="O69" s="6"/>
+      <c r="P69" s="6"/>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" s="6"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="6"/>
+      <c r="K70" s="6"/>
+      <c r="L70" s="6"/>
+      <c r="M70" s="6"/>
+      <c r="N70" s="6"/>
+      <c r="O70" s="6"/>
+      <c r="P70" s="6"/>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" s="6"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="6"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="6"/>
+      <c r="M71" s="6"/>
+      <c r="N71" s="6"/>
+      <c r="O71" s="6"/>
+      <c r="P71" s="6"/>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" s="6"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
+      <c r="M72" s="6"/>
+      <c r="N72" s="6"/>
+      <c r="O72" s="6"/>
+      <c r="P72" s="6"/>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" s="6"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
+      <c r="J73" s="6"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="6"/>
+      <c r="M73" s="6"/>
+      <c r="N73" s="6"/>
+      <c r="O73" s="6"/>
+      <c r="P73" s="6"/>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74" s="6"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="6"/>
+      <c r="O74" s="6"/>
+      <c r="P74" s="6"/>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" s="6"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="6"/>
+      <c r="J75" s="6"/>
+      <c r="K75" s="6"/>
+      <c r="L75" s="6"/>
+      <c r="M75" s="6"/>
+      <c r="N75" s="6"/>
+      <c r="O75" s="6"/>
+      <c r="P75" s="6"/>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" s="6"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="6"/>
+      <c r="J76" s="6"/>
+      <c r="K76" s="6"/>
+      <c r="L76" s="6"/>
+      <c r="M76" s="6"/>
+      <c r="N76" s="6"/>
+      <c r="O76" s="6"/>
+      <c r="P76" s="6"/>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" s="6"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="6"/>
+      <c r="J77" s="6"/>
+      <c r="K77" s="6"/>
+      <c r="L77" s="6"/>
+      <c r="M77" s="6"/>
+      <c r="N77" s="6"/>
+      <c r="O77" s="6"/>
+      <c r="P77" s="6"/>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A78" s="6"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
+      <c r="M78" s="6"/>
+      <c r="N78" s="6"/>
+      <c r="O78" s="6"/>
+      <c r="P78" s="6"/>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79" s="6"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="6"/>
+      <c r="J79" s="6"/>
+      <c r="K79" s="6"/>
+      <c r="L79" s="6"/>
+      <c r="M79" s="6"/>
+      <c r="N79" s="6"/>
+      <c r="O79" s="6"/>
+      <c r="P79" s="6"/>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A80" s="6"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
+      <c r="K80" s="6"/>
+      <c r="L80" s="6"/>
+      <c r="M80" s="6"/>
+      <c r="N80" s="6"/>
+      <c r="O80" s="6"/>
+      <c r="P80" s="6"/>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A81" s="6"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6"/>
+      <c r="J81" s="6"/>
+      <c r="K81" s="6"/>
+      <c r="L81" s="6"/>
+      <c r="M81" s="6"/>
+      <c r="N81" s="6"/>
+      <c r="O81" s="6"/>
+      <c r="P81" s="6"/>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A82" s="6"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6"/>
+      <c r="J82" s="6"/>
+      <c r="K82" s="6"/>
+      <c r="L82" s="6"/>
+      <c r="M82" s="6"/>
+      <c r="N82" s="6"/>
+      <c r="O82" s="6"/>
+      <c r="P82" s="6"/>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A83" s="6"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="6"/>
+      <c r="J83" s="6"/>
+      <c r="K83" s="6"/>
+      <c r="L83" s="6"/>
+      <c r="M83" s="6"/>
+      <c r="N83" s="6"/>
+      <c r="O83" s="6"/>
+      <c r="P83" s="6"/>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A84" s="6"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6"/>
+      <c r="J84" s="6"/>
+      <c r="K84" s="6"/>
+      <c r="L84" s="6"/>
+      <c r="M84" s="6"/>
+      <c r="N84" s="6"/>
+      <c r="O84" s="6"/>
+      <c r="P84" s="6"/>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A85" s="6"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6"/>
+      <c r="J85" s="6"/>
+      <c r="K85" s="6"/>
+      <c r="L85" s="6"/>
+      <c r="M85" s="6"/>
+      <c r="N85" s="6"/>
+      <c r="O85" s="6"/>
+      <c r="P85" s="6"/>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A86" s="6"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="6"/>
+      <c r="J86" s="6"/>
+      <c r="K86" s="6"/>
+      <c r="L86" s="6"/>
+      <c r="M86" s="6"/>
+      <c r="N86" s="6"/>
+      <c r="O86" s="6"/>
+      <c r="P86" s="6"/>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A87" s="6"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="6"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="6"/>
+      <c r="J87" s="6"/>
+      <c r="K87" s="6"/>
+      <c r="L87" s="6"/>
+      <c r="M87" s="6"/>
+      <c r="N87" s="6"/>
+      <c r="O87" s="6"/>
+      <c r="P87" s="6"/>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A88" s="6"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="6"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="6"/>
+      <c r="J88" s="6"/>
+      <c r="K88" s="6"/>
+      <c r="L88" s="6"/>
+      <c r="M88" s="6"/>
+      <c r="N88" s="6"/>
+      <c r="O88" s="6"/>
+      <c r="P88" s="6"/>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A89" s="6"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="6"/>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="6"/>
+      <c r="J89" s="6"/>
+      <c r="K89" s="6"/>
+      <c r="L89" s="6"/>
+      <c r="M89" s="6"/>
+      <c r="N89" s="6"/>
+      <c r="O89" s="6"/>
+      <c r="P89" s="6"/>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A90" s="6"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="6"/>
+      <c r="L90" s="6"/>
+      <c r="M90" s="6"/>
+      <c r="N90" s="6"/>
+      <c r="O90" s="6"/>
+      <c r="P90" s="6"/>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A91" s="6"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="6"/>
+      <c r="J91" s="6"/>
+      <c r="K91" s="6"/>
+      <c r="L91" s="6"/>
+      <c r="M91" s="6"/>
+      <c r="N91" s="6"/>
+      <c r="O91" s="6"/>
+      <c r="P91" s="6"/>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A92" s="6"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="6"/>
+      <c r="J92" s="6"/>
+      <c r="K92" s="6"/>
+      <c r="L92" s="6"/>
+      <c r="M92" s="6"/>
+      <c r="N92" s="6"/>
+      <c r="O92" s="6"/>
+      <c r="P92" s="6"/>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A93" s="6"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="6"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="6"/>
+      <c r="J93" s="6"/>
+      <c r="K93" s="6"/>
+      <c r="L93" s="6"/>
+      <c r="M93" s="6"/>
+      <c r="N93" s="6"/>
+      <c r="O93" s="6"/>
+      <c r="P93" s="6"/>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A94" s="6"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="6"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="6"/>
+      <c r="L94" s="6"/>
+      <c r="M94" s="6"/>
+      <c r="N94" s="6"/>
+      <c r="O94" s="6"/>
+      <c r="P94" s="6"/>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A95" s="6"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="6"/>
+      <c r="J95" s="6"/>
+      <c r="K95" s="6"/>
+      <c r="L95" s="6"/>
+      <c r="M95" s="6"/>
+      <c r="N95" s="6"/>
+      <c r="O95" s="6"/>
+      <c r="P95" s="6"/>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A96" s="6"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="6"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="6"/>
+      <c r="J96" s="6"/>
+      <c r="K96" s="6"/>
+      <c r="L96" s="6"/>
+      <c r="M96" s="6"/>
+      <c r="N96" s="6"/>
+      <c r="O96" s="6"/>
+      <c r="P96" s="6"/>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A97" s="6"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="6"/>
+      <c r="J97" s="6"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="6"/>
+      <c r="M97" s="6"/>
+      <c r="N97" s="6"/>
+      <c r="O97" s="6"/>
+      <c r="P97" s="6"/>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A98" s="6"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6"/>
+      <c r="J98" s="6"/>
+      <c r="K98" s="6"/>
+      <c r="L98" s="6"/>
+      <c r="M98" s="6"/>
+      <c r="N98" s="6"/>
+      <c r="O98" s="6"/>
+      <c r="P98" s="6"/>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A99" s="6"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="6"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="6"/>
+      <c r="M99" s="6"/>
+      <c r="N99" s="6"/>
+      <c r="O99" s="6"/>
+      <c r="P99" s="6"/>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A100" s="6"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6"/>
+      <c r="J100" s="6"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="6"/>
+      <c r="M100" s="6"/>
+      <c r="N100" s="6"/>
+      <c r="O100" s="6"/>
+      <c r="P100" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:P31"/>
+    <mergeCell ref="A32:P100"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1515,22 +4300,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>3</v>
@@ -1545,19 +4330,13 @@
         <v>6</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>9</v>
-      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -1569,15 +4348,9 @@
       <c r="L2" s="4"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -1589,15 +4362,9 @@
       <c r="L3" s="4"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -1609,15 +4376,9 @@
       <c r="L4" s="4"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -1629,15 +4390,9 @@
       <c r="L5" s="4"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -1649,15 +4404,9 @@
       <c r="L6" s="4"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -1669,15 +4418,9 @@
       <c r="L7" s="4"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
@@ -1689,15 +4432,9 @@
       <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -1709,15 +4446,9 @@
       <c r="L9" s="4"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -1729,15 +4460,9 @@
       <c r="L10" s="4"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -1749,15 +4474,9 @@
       <c r="L11" s="4"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -1769,15 +4488,9 @@
       <c r="L12" s="4"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -1789,15 +4502,9 @@
       <c r="L13" s="4"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -1809,15 +4516,9 @@
       <c r="L14" s="4"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -1829,15 +4530,9 @@
       <c r="L15" s="4"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>31</v>
-      </c>
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
@@ -1849,15 +4544,9 @@
       <c r="L16" s="4"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>31</v>
-      </c>
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
@@ -1869,15 +4558,9 @@
       <c r="L17" s="4"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="5">
-        <v>22</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -1889,15 +4572,9 @@
       <c r="L18" s="4"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="5">
-        <v>22</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -1909,15 +4586,9 @@
       <c r="L19" s="4"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="5">
-        <v>22</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
@@ -1929,15 +4600,9 @@
       <c r="L20" s="4"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="5">
-        <v>22</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -1949,15 +4614,9 @@
       <c r="L21" s="4"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="5">
-        <v>25</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="A22" s="4"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -1969,15 +4628,9 @@
       <c r="L22" s="4"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="5">
-        <v>25</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="A23" s="4"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
@@ -1989,15 +4642,9 @@
       <c r="L23" s="4"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="5">
-        <v>26</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>42</v>
-      </c>
+      <c r="A24" s="4"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -2009,15 +4656,9 @@
       <c r="L24" s="4"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="5">
-        <v>26</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>42</v>
-      </c>
+      <c r="A25" s="4"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -2029,15 +4670,9 @@
       <c r="L25" s="4"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="5">
-        <v>30</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="A26" s="4"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
@@ -2049,15 +4684,9 @@
       <c r="L26" s="4"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="5">
-        <v>30</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="A27" s="4"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -2069,15 +4698,9 @@
       <c r="L27" s="4"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28" s="5">
-        <v>30</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="A28" s="4"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -2089,15 +4712,9 @@
       <c r="L28" s="4"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" s="5">
-        <v>30</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="A29" s="4"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
@@ -2109,15 +4726,9 @@
       <c r="L29" s="4"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" s="5">
-        <v>30</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="A30" s="4"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -2129,15 +4740,9 @@
       <c r="L30" s="4"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" s="5">
-        <v>30</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="A31" s="4"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
@@ -2149,15 +4754,9 @@
       <c r="L31" s="4"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32" s="5">
-        <v>33</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="A32" s="4"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
@@ -2169,15 +4768,9 @@
       <c r="L32" s="4"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B33" s="5">
-        <v>33</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="A33" s="4"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -2189,15 +4782,9 @@
       <c r="L33" s="4"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B34" s="5">
-        <v>33</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="A34" s="4"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
@@ -2209,15 +4796,9 @@
       <c r="L34" s="4"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B35" s="5">
-        <v>33</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="A35" s="4"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
@@ -2229,15 +4810,9 @@
       <c r="L35" s="4"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" s="5">
-        <v>33</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="A36" s="4"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
@@ -2249,15 +4824,9 @@
       <c r="L36" s="4"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B37" s="5">
-        <v>33</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="A37" s="4"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -2269,15 +4838,9 @@
       <c r="L37" s="4"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B38" s="5">
-        <v>37</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>59</v>
-      </c>
+      <c r="A38" s="4"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
@@ -2289,15 +4852,9 @@
       <c r="L38" s="4"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B39" s="5">
-        <v>37</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>59</v>
-      </c>
+      <c r="A39" s="4"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -2309,15 +4866,9 @@
       <c r="L39" s="4"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B40" s="5">
-        <v>54</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>62</v>
-      </c>
+      <c r="A40" s="4"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -2329,15 +4880,9 @@
       <c r="L40" s="4"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B41" s="5">
-        <v>54</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>62</v>
-      </c>
+      <c r="A41" s="4"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
@@ -2349,15 +4894,9 @@
       <c r="L41" s="4"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B42" s="5">
-        <v>102</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="A42" s="4"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
@@ -2369,15 +4908,9 @@
       <c r="L42" s="4"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B43" s="5">
-        <v>102</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="A43" s="4"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
@@ -2389,15 +4922,9 @@
       <c r="L43" s="4"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B44" s="5">
-        <v>102</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="A44" s="4"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
@@ -2409,15 +4936,9 @@
       <c r="L44" s="4"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B45" s="5">
-        <v>102</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="A45" s="4"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
@@ -2429,15 +4950,9 @@
       <c r="L45" s="4"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B46" s="5">
-        <v>115</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>70</v>
-      </c>
+      <c r="A46" s="4"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
@@ -2449,15 +4964,9 @@
       <c r="L46" s="4"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B47" s="5">
-        <v>115</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>70</v>
-      </c>
+      <c r="A47" s="4"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
@@ -2469,15 +4978,9 @@
       <c r="L47" s="4"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B48" s="5">
-        <v>115</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>70</v>
-      </c>
+      <c r="A48" s="4"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
@@ -2489,15 +4992,9 @@
       <c r="L48" s="4"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B49" s="5">
-        <v>115</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>70</v>
-      </c>
+      <c r="A49" s="4"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
@@ -2509,15 +5006,9 @@
       <c r="L49" s="4"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B50" s="5">
-        <v>115</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>70</v>
-      </c>
+      <c r="A50" s="4"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
@@ -2529,15 +5020,9 @@
       <c r="L50" s="4"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B51" s="5">
-        <v>115</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>70</v>
-      </c>
+      <c r="A51" s="4"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>

--- a/Workflows/Chemical validation/Level0_Templates/XXXX_XX_ANIONS.xlsx
+++ b/Workflows/Chemical validation/Level0_Templates/XXXX_XX_ANIONS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jtorrens\ICP\repoGitLab\lifewatch-vre\Workflows\Chemical validation\Level0_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F5C08B-1008-44ED-B98E-793ADEC59EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EF874F-88F1-462C-89D4-58F02B69E063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3FD923B0-A352-4B39-804E-C5D1C21F4722}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3FD923B0-A352-4B39-804E-C5D1C21F4722}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="2" r:id="rId1"/>
@@ -557,7 +557,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Use the standardised ICP sample code for the plot and subprogramme. The code combines the plot number, the species abbreviation, the collection type (INT = interior/throughfall, EXT = exterior/bulk deposition) and any additional qualifier: INT         = throughfall (interior of the forest) EXT         = bulk open-field deposition (exterior) NIEVE       = snow sample LIX 20      = soil lysimeter at 20 cm depth LIX 60      = soil lysimeter at 60 cm depth LIX G 20    = gravity lysimeter at 20 cm depth LIX G 60    = gravity lysimeter at 60 cm depth</a:t>
+            <a:t>Use the standardised ICP sample code for the plot and subprogramme. The code could combines the plot number, the species abbreviation, the collection type (INT = interior/throughfall, EXT = exterior/bulk deposition) and any additional qualifier: INT         = throughfall (interior of the forest) EXT         = bulk open-field deposition (exterior) NIEVE       = snow sample LIX 20      = soil lysimeter at 20 cm depth LIX 60      = soil lysimeter at 60 cm depth LIX G 20    = gravity lysimeter at 20 cm depth LIX G 60    = gravity lysimeter at 60 cm depth</a:t>
           </a:r>
           <a:endParaRPr lang="es-ES">
             <a:effectLst/>
@@ -681,6 +681,18 @@
             <a:t>- How to fill: </a:t>
           </a:r>
           <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>You could u</a:t>
+          </a:r>
+          <a:r>
             <a:rPr lang="en-US" sz="1100">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
@@ -690,7 +702,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Use the official ICP plot number (e.g. 05, 22, 115). Do not include leading zeros beyond the standard format.</a:t>
+            <a:t>se the official ICP plot number (e.g. 05, 22, 115). Do not include leading zeros beyond the standard format.</a:t>
           </a:r>
           <a:endParaRPr lang="es-ES">
             <a:effectLst/>
